--- a/students/شفیعیsum2.3ok.xlsx
+++ b/students/شفیعیsum2.3ok.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27328"/>
   <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF2A3613-DCA1-4015-B0E2-708088B42C95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20730" windowHeight="11760"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,9 +28,6 @@
     <t>نام</t>
   </si>
   <si>
-    <t>نام خانوادگي</t>
-  </si>
-  <si>
     <t>تلفن</t>
   </si>
   <si>
@@ -130,24 +128,27 @@
   </si>
   <si>
     <t>sum 2.3</t>
+  </si>
+  <si>
+    <t>نام خانوادگی</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -198,15 +199,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -493,25 +491,25 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H15"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.09765625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.5703125" style="2" customWidth="1"/>
-    <col min="2" max="2" width="9.42578125" style="2" customWidth="1"/>
-    <col min="3" max="3" width="10.7109375" style="2" customWidth="1"/>
-    <col min="4" max="4" width="9.7109375" style="5" customWidth="1"/>
+    <col min="1" max="1" width="10.59765625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="9.3984375" style="2" customWidth="1"/>
+    <col min="3" max="3" width="10.69921875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="9.69921875" style="4" customWidth="1"/>
     <col min="5" max="5" width="13" style="2" customWidth="1"/>
-    <col min="6" max="6" width="13.85546875" style="2" customWidth="1"/>
-    <col min="7" max="7" width="47.85546875" style="2" customWidth="1"/>
-    <col min="8" max="16384" width="9.140625" style="2"/>
+    <col min="6" max="6" width="13.8984375" style="2" customWidth="1"/>
+    <col min="7" max="7" width="47.8984375" style="2" customWidth="1"/>
+    <col min="8" max="16384" width="9.09765625" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -522,34 +520,34 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="7"/>
+      <c r="H1" s="6"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>6856</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>35</v>
+      <c r="D2" s="3" t="s">
+        <v>34</v>
       </c>
       <c r="E2" s="1">
         <v>33444470</v>
@@ -564,13 +562,13 @@
         <v>6874</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>35</v>
+      <c r="D3" s="3" t="s">
+        <v>34</v>
       </c>
       <c r="E3" s="1">
         <v>9963899360</v>
@@ -583,13 +581,13 @@
         <v>8337</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>35</v>
+      <c r="D4" s="3" t="s">
+        <v>34</v>
       </c>
       <c r="E4" s="1">
         <v>9383789964</v>
@@ -600,19 +598,19 @@
       <c r="G4" s="1"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="3">
+      <c r="A5" s="1">
         <v>8378</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E5" s="3">
+      <c r="D5" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E5" s="1">
         <v>9192417278</v>
       </c>
       <c r="F5" s="1">
@@ -621,64 +619,64 @@
       <c r="G5" s="1"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="3">
+      <c r="A6" s="1">
         <v>8379</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="D6" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E6" s="1">
+        <v>9194433940</v>
+      </c>
+      <c r="F6" s="1">
+        <v>9922323705</v>
+      </c>
+      <c r="G6" s="1"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>9894</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D6" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E6" s="3">
-        <v>9194433940</v>
-      </c>
-      <c r="F6" s="3">
-        <v>9922323705</v>
-      </c>
-      <c r="G6" s="1"/>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="3">
-        <v>9894</v>
-      </c>
-      <c r="B7" s="3" t="s">
+      <c r="C7" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C7" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>35</v>
+      <c r="D7" s="3" t="s">
+        <v>34</v>
       </c>
       <c r="E7" s="1">
         <v>9908750494</v>
       </c>
-      <c r="F7" s="3">
+      <c r="F7" s="1">
         <v>9196792483</v>
       </c>
       <c r="G7" s="1"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="3">
+      <c r="A8" s="1">
         <v>9187</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C8" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E8" s="3">
+      <c r="D8" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E8" s="1">
         <v>9191414931</v>
       </c>
-      <c r="F8" s="3">
+      <c r="F8" s="1">
         <v>9193414932</v>
       </c>
       <c r="G8" s="1">
@@ -690,13 +688,13 @@
         <v>9729</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>35</v>
+        <v>6</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>34</v>
       </c>
       <c r="E9" s="1">
         <v>9059690208</v>
@@ -711,13 +709,13 @@
         <v>11081</v>
       </c>
       <c r="B10" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C10" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>36</v>
+      <c r="D10" s="3" t="s">
+        <v>35</v>
       </c>
       <c r="E10" s="1">
         <v>9196112619</v>
@@ -732,13 +730,13 @@
         <v>8906</v>
       </c>
       <c r="B11" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C11" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>35</v>
+      <c r="D11" s="4" t="s">
+        <v>34</v>
       </c>
       <c r="E11" s="2">
         <v>9191450662</v>
@@ -752,13 +750,13 @@
         <v>10344</v>
       </c>
       <c r="B12" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C12" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>35</v>
+      <c r="D12" s="4" t="s">
+        <v>34</v>
       </c>
       <c r="E12" s="2">
         <v>9104767662</v>
@@ -772,13 +770,13 @@
         <v>111067</v>
       </c>
       <c r="B13" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C13" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>35</v>
+      <c r="D13" s="4" t="s">
+        <v>34</v>
       </c>
       <c r="E13" s="2">
         <v>9102410081</v>
@@ -792,13 +790,13 @@
         <v>111845</v>
       </c>
       <c r="B14" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C14" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>36</v>
+      <c r="D14" s="4" t="s">
+        <v>35</v>
       </c>
       <c r="E14" s="2">
         <v>9104862599</v>
@@ -812,13 +810,13 @@
         <v>111517</v>
       </c>
       <c r="B15" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C15" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C15" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>36</v>
+      <c r="D15" s="4" t="s">
+        <v>35</v>
       </c>
       <c r="E15" s="2">
         <v>9121410913</v>
